--- a/DATA MASTER/Maret-2025.xlsx
+++ b/DATA MASTER/Maret-2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BAM\Downloads\linknet-main\DATA MASTER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODEX PROJECT\Dashboard LinkNet\DATA MASTER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{584242EE-EDE3-4A3F-B8D7-076FE32A4027}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2268CA-4ED5-4ECD-8CE0-A251DFD00370}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6375" yWindow="2835" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="report-mikhmon-mar2026" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="318">
   <si>
     <t>№</t>
   </si>
@@ -895,15 +895,9 @@
     <t>E4JTL</t>
   </si>
   <si>
-    <t>mar/02/2025</t>
-  </si>
-  <si>
     <t>H5LGB</t>
   </si>
   <si>
-    <t>mar/04/2025</t>
-  </si>
-  <si>
     <t>H4SYF</t>
   </si>
   <si>
@@ -913,21 +907,12 @@
     <t>up-774-06.09.23-</t>
   </si>
   <si>
-    <t>mar/05/2025</t>
-  </si>
-  <si>
     <t>H5DRW</t>
   </si>
   <si>
-    <t>mar/09/2025</t>
-  </si>
-  <si>
     <t>H5599</t>
   </si>
   <si>
-    <t>mar/12/2025</t>
-  </si>
-  <si>
     <t>H1X2F</t>
   </si>
   <si>
@@ -937,24 +922,15 @@
     <t>H1RGM</t>
   </si>
   <si>
-    <t>Mar/12/2025</t>
-  </si>
-  <si>
     <t>H129B</t>
   </si>
   <si>
-    <t>Mar/13/2025</t>
-  </si>
-  <si>
     <t>H5Z5Y</t>
   </si>
   <si>
     <t>H1TG4</t>
   </si>
   <si>
-    <t>Mar/14/2025</t>
-  </si>
-  <si>
     <t>H5VFB</t>
   </si>
   <si>
@@ -964,48 +940,27 @@
     <t>H19BG</t>
   </si>
   <si>
-    <t>Mar/15/2025</t>
-  </si>
-  <si>
     <t>H599V</t>
   </si>
   <si>
-    <t>Mar/17/2025</t>
-  </si>
-  <si>
     <t>H4XT3</t>
   </si>
   <si>
-    <t>Mar/20/2025</t>
-  </si>
-  <si>
     <t>H4XGZ</t>
   </si>
   <si>
-    <t>Mar/21/2025</t>
-  </si>
-  <si>
     <t>H4R53</t>
   </si>
   <si>
-    <t>Mar/22/2025</t>
-  </si>
-  <si>
     <t>H4BW8</t>
   </si>
   <si>
     <t>H1RDG</t>
   </si>
   <si>
-    <t>Mar/23/2025</t>
-  </si>
-  <si>
     <t>H4KEK</t>
   </si>
   <si>
-    <t>Mar/30/2025</t>
-  </si>
-  <si>
     <t>H4DP7</t>
   </si>
   <si>
@@ -1015,13 +970,13 @@
     <t>H4WUS</t>
   </si>
   <si>
-    <t>Mar/31/2025</t>
-  </si>
-  <si>
     <t>H4WXR</t>
   </si>
   <si>
     <t>H53P2</t>
+  </si>
+  <si>
+    <t>Mar/01/2025</t>
   </si>
 </sst>
 </file>
@@ -1383,13 +1338,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>290</v>
+        <v>317</v>
       </c>
       <c r="C2" s="5">
         <v>0.49952546296296302</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>84</v>
@@ -1408,19 +1363,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="C3" s="5">
         <v>0.3008912037037037</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>293</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>295</v>
       </c>
       <c r="G3" s="3">
         <v>1000</v>
@@ -1433,13 +1388,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="C4" s="5">
         <v>0.12623842592592593</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>84</v>
@@ -1458,13 +1413,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
       <c r="C5" s="5">
         <v>0.26324074074074072</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>84</v>
@@ -1483,13 +1438,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="C6" s="5">
         <v>0.66945601851851855</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>206</v>
@@ -1508,13 +1463,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="C7" s="5">
         <v>0.66961805555555554</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>206</v>
@@ -1533,13 +1488,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="C8" s="5">
         <v>0.67532407407407413</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>206</v>
@@ -1558,13 +1513,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="C9" s="5">
         <v>0.91618055555555555</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>206</v>
@@ -1583,13 +1538,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="C10" s="5">
         <v>0.11071759259259258</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>84</v>
@@ -1608,13 +1563,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="C11" s="5">
         <v>0.26068287037037036</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>206</v>
@@ -1633,13 +1588,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="C12" s="5">
         <v>0.11261574074074072</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>84</v>
@@ -1658,19 +1613,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="C13" s="5">
         <v>0.84876157407407404</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G13" s="3">
         <v>1000</v>
@@ -1683,13 +1638,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="C14" s="5">
         <v>0.98268518518518511</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>206</v>
@@ -1708,13 +1663,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C15" s="5">
         <v>0.25178240740740737</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>84</v>
@@ -1733,19 +1688,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C16" s="5">
         <v>0.81909722222222225</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G16" s="3">
         <v>1000</v>
@@ -1757,20 +1712,20 @@
       <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="4" t="s">
         <v>317</v>
       </c>
       <c r="C17" s="7">
         <v>0.38517361111111109</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G17" s="8">
         <v>1000</v>
@@ -1783,19 +1738,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C18" s="5">
         <v>0.15991898148148148</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G18" s="3">
         <v>1000</v>
@@ -1808,19 +1763,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C19" s="5">
         <v>0.4256597222222222</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G19" s="3">
         <v>1000</v>
@@ -1833,13 +1788,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C20" s="5">
         <v>0.42645833333333333</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>206</v>
@@ -1858,19 +1813,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="C21" s="5">
         <v>0.38461805555555556</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G21" s="3">
         <v>1000</v>
@@ -1883,19 +1838,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="C22" s="5">
         <v>0.4324305555555556</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G22" s="3">
         <v>1000</v>
@@ -1908,19 +1863,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="C23" s="5">
         <v>0.87601851851851853</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G23" s="3">
         <v>1000</v>
@@ -1933,19 +1888,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="C24" s="5">
         <v>0.87807870370370367</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G24" s="3">
         <v>1000</v>
@@ -1958,19 +1913,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="C25" s="5">
         <v>0.77832175925925917</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G25" s="3">
         <v>1000</v>
@@ -1982,14 +1937,14 @@
       <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>330</v>
+      <c r="B26" s="4" t="s">
+        <v>317</v>
       </c>
       <c r="C26" s="7">
         <v>0.89819444444444441</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>84</v>

--- a/DATA MASTER/Maret-2025.xlsx
+++ b/DATA MASTER/Maret-2025.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODEX PROJECT\Dashboard LinkNet\DATA MASTER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2268CA-4ED5-4ECD-8CE0-A251DFD00370}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A05260-F43A-4EFB-865A-C3790574E957}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="report-mikhmon-mar2026" sheetId="1" r:id="rId1"/>
+    <sheet name="report-mikhmon-mar2025" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'report-mikhmon-mar2026'!$A$1:$G$1056</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'report-mikhmon-mar2025'!$A$1:$G$1056</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
